--- a/figures/xlsx/figure3B.xlsx
+++ b/figures/xlsx/figure3B.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pascal/Dropbox (Brown)/web/p-hacking/figures/xlsx/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96318285-165A-7942-95EC-1635EF2D4382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27740" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Figure 3B" sheetId="2" r:id="rId3"/>
+    <sheet name="Figure 3B" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Completion probability</t>
   </si>
@@ -24,26 +30,52 @@
   <si>
     <t>Number of experiments under robust critical value</t>
   </si>
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>figure3B.m</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CAE4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,1153 +83,1481 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C102"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C103"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="true"/>
-    <col min="2" max="2" width="11.7109375" customWidth="true"/>
-    <col min="3" max="3" width="11.7109375" customWidth="true"/>
+    <col min="1" max="1" width="18.83203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="24.1640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.1640625" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:3" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
         <v>0</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C3" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
         <v>0.01</v>
       </c>
-      <c r="B3" s="0">
+      <c r="B4" s="4">
         <v>1.0095911155981827</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C4" s="5">
         <v>1.0095959595959596</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
         <v>0.02</v>
       </c>
-      <c r="B4" s="0">
+      <c r="B5" s="4">
         <v>1.019367991845056</v>
       </c>
-      <c r="C4" s="0">
+      <c r="C5" s="5">
         <v>1.0193877551020409</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0">
-        <v>0.029999999999999999</v>
-      </c>
-      <c r="B5" s="0">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="B6" s="4">
         <v>1.029336078229542</v>
       </c>
-      <c r="C5" s="0">
+      <c r="C6" s="5">
         <v>1.0293814432989692</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0">
-        <v>0.040000000000000001</v>
-      </c>
-      <c r="B6" s="0">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="B7" s="4">
         <v>1.0395010395010396</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C7" s="5">
         <v>1.0395833333333333</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="B7" s="0">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="B8" s="4">
         <v>1.0498687664041995</v>
       </c>
-      <c r="C7" s="0">
+      <c r="C8" s="5">
         <v>1.05</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0">
-        <v>0.059999999999999998</v>
-      </c>
-      <c r="B8" s="0">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="B9" s="4">
         <v>1.0604453870625663</v>
       </c>
-      <c r="C8" s="0">
+      <c r="C9" s="5">
         <v>1.0606382978723405</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0">
-        <v>0.070000000000000007</v>
-      </c>
-      <c r="B9" s="0">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="B10" s="4">
         <v>1.0712372790573113</v>
       </c>
-      <c r="C9" s="0">
+      <c r="C10" s="5">
         <v>1.071505376344086</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0">
-        <v>0.080000000000000002</v>
-      </c>
-      <c r="B10" s="0">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="B11" s="4">
         <v>1.0822510822510822</v>
       </c>
-      <c r="C10" s="0">
+      <c r="C11" s="5">
         <v>1.0826086956521739</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0">
-        <v>0.089999999999999997</v>
-      </c>
-      <c r="B11" s="0">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="B12" s="4">
         <v>1.0934937124111537</v>
       </c>
-      <c r="C11" s="0">
+      <c r="C12" s="5">
         <v>1.0939560439560441</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="B12" s="0">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="B13" s="4">
         <v>1.1049723756906078</v>
       </c>
-      <c r="C12" s="0">
+      <c r="C13" s="5">
         <v>1.1055555555555556</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
         <v>0.11</v>
       </c>
-      <c r="B13" s="0">
+      <c r="B14" s="4">
         <v>1.1166945840312674</v>
       </c>
-      <c r="C13" s="0">
+      <c r="C14" s="5">
         <v>1.1174157303370786</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="0">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
         <v>0.12</v>
       </c>
-      <c r="B14" s="0">
+      <c r="B15" s="4">
         <v>1.1286681715575622</v>
       </c>
-      <c r="C14" s="0">
+      <c r="C15" s="5">
         <v>1.1295454545454546</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="0">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
         <v>0.13</v>
       </c>
-      <c r="B15" s="0">
+      <c r="B16" s="4">
         <v>1.1409013120365088</v>
       </c>
-      <c r="C15" s="0">
+      <c r="C16" s="5">
         <v>1.1419540229885059</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="0">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="B16" s="0">
+      <c r="B17" s="4">
         <v>1.1534025374855825</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C17" s="5">
         <v>1.1546511627906977</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="0">
-        <v>0.14999999999999999</v>
-      </c>
-      <c r="B17" s="0">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="B18" s="4">
         <v>1.1661807580174925</v>
       </c>
-      <c r="C17" s="0">
+      <c r="C18" s="5">
         <v>1.1676470588235295</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
         <v>0.16</v>
       </c>
-      <c r="B18" s="0">
+      <c r="B19" s="4">
         <v>1.179245283018868</v>
       </c>
-      <c r="C18" s="0">
+      <c r="C19" s="5">
         <v>1.180952380952381</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="0">
-        <v>0.17000000000000001</v>
-      </c>
-      <c r="B19" s="0">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
+        <v>0.17</v>
+      </c>
+      <c r="B20" s="4">
         <v>1.1926058437686344</v>
       </c>
-      <c r="C19" s="0">
+      <c r="C20" s="5">
         <v>1.1945783132530121</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="0">
-        <v>0.17999999999999999</v>
-      </c>
-      <c r="B20" s="0">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="4">
+        <v>0.18</v>
+      </c>
+      <c r="B21" s="4">
         <v>1.2062726176115803</v>
       </c>
-      <c r="C20" s="0">
+      <c r="C21" s="5">
         <v>1.2085365853658536</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="0">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
         <v>0.19</v>
       </c>
-      <c r="B21" s="0">
+      <c r="B22" s="4">
         <v>1.2202562538133008</v>
       </c>
-      <c r="C21" s="0">
+      <c r="C22" s="5">
         <v>1.2228395061728394</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="0">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="B22" s="0">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="B23" s="4">
         <v>1.2345679012345678</v>
       </c>
-      <c r="C22" s="0">
+      <c r="C23" s="5">
         <v>1.2374999999999998</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="0">
-        <v>0.20999999999999999</v>
-      </c>
-      <c r="B23" s="0">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="4">
+        <v>0.21</v>
+      </c>
+      <c r="B24" s="4">
         <v>1.2492192379762648</v>
       </c>
-      <c r="C23" s="0">
+      <c r="C24" s="5">
         <v>1.2525316455696203</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="0">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="4">
         <v>0.22</v>
       </c>
-      <c r="B24" s="0">
+      <c r="B25" s="4">
         <v>1.2642225031605563</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C25" s="5">
         <v>1.2679487179487179</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="0">
-        <v>0.23000000000000001</v>
-      </c>
-      <c r="B25" s="0">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="4">
+        <v>0.23</v>
+      </c>
+      <c r="B26" s="4">
         <v>1.2795905310300704</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C26" s="5">
         <v>1.2837662337662339</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="0">
-        <v>0.23999999999999999</v>
-      </c>
-      <c r="B26" s="0">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="4">
+        <v>0.24</v>
+      </c>
+      <c r="B27" s="4">
         <v>1.2953367875647668</v>
       </c>
-      <c r="C26" s="0">
+      <c r="C27" s="5">
         <v>1.3</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="0">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="4">
         <v>0.25</v>
       </c>
-      <c r="B27" s="0">
+      <c r="B28" s="4">
         <v>1.3114754098360657</v>
       </c>
-      <c r="C27" s="0">
+      <c r="C28" s="5">
         <v>1.3166666666666667</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="0">
-        <v>0.26000000000000001</v>
-      </c>
-      <c r="B28" s="0">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="4">
+        <v>0.26</v>
+      </c>
+      <c r="B29" s="4">
         <v>1.3280212483399734</v>
       </c>
-      <c r="C28" s="0">
+      <c r="C29" s="5">
         <v>1.3337837837837838</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="0">
-        <v>0.27000000000000002</v>
-      </c>
-      <c r="B29" s="0">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="4">
+        <v>0.27</v>
+      </c>
+      <c r="B30" s="4">
         <v>1.3449899125756557</v>
       </c>
-      <c r="C29" s="0">
+      <c r="C30" s="5">
         <v>1.3513698630136988</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="0">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="4">
         <v>0.28000000000000003</v>
       </c>
-      <c r="B30" s="0">
+      <c r="B31" s="4">
         <v>1.3623978201634879</v>
       </c>
-      <c r="C30" s="0">
+      <c r="C31" s="5">
         <v>1.3694444444444445</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="0">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="4">
         <v>0.28999999999999998</v>
       </c>
-      <c r="B31" s="0">
+      <c r="B32" s="4">
         <v>1.3802622498274673</v>
       </c>
-      <c r="C31" s="0">
+      <c r="C32" s="5">
         <v>1.3880281690140845</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="B32" s="0">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="B33" s="4">
         <v>1.3986013986013985</v>
       </c>
-      <c r="C32" s="0">
+      <c r="C33" s="5">
         <v>1.4071428571428573</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="0">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="4">
         <v>0.31</v>
       </c>
-      <c r="B33" s="0">
+      <c r="B34" s="4">
         <v>1.4174344436569808</v>
       </c>
-      <c r="C33" s="0">
+      <c r="C34" s="5">
         <v>1.4268115942028987</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="0">
-        <v>0.32000000000000001</v>
-      </c>
-      <c r="B34" s="0">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="4">
+        <v>0.32</v>
+      </c>
+      <c r="B35" s="4">
         <v>1.4367816091954024</v>
       </c>
-      <c r="C34" s="0">
+      <c r="C35" s="5">
         <v>1.447058823529412</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="0">
-        <v>0.33000000000000002</v>
-      </c>
-      <c r="B35" s="0">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="4">
+        <v>0.33</v>
+      </c>
+      <c r="B36" s="4">
         <v>1.4566642388929352</v>
       </c>
-      <c r="C35" s="0">
+      <c r="C36" s="5">
         <v>1.4679104477611942</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="0">
-        <v>0.34000000000000002</v>
-      </c>
-      <c r="B36" s="0">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="4">
+        <v>0.34</v>
+      </c>
+      <c r="B37" s="4">
         <v>1.4771048744460855</v>
       </c>
-      <c r="C36" s="0">
+      <c r="C37" s="5">
         <v>1.4893939393939395</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="0">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="4">
         <v>0.35000000000000003</v>
       </c>
-      <c r="B37" s="0">
+      <c r="B38" s="4">
         <v>1.4981273408239701</v>
       </c>
-      <c r="C37" s="0">
+      <c r="C38" s="5">
         <v>1.5115384615384617</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="0">
-        <v>0.35999999999999999</v>
-      </c>
-      <c r="B38" s="0">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="4">
+        <v>0.36</v>
+      </c>
+      <c r="B39" s="4">
         <v>1.519756838905775</v>
       </c>
-      <c r="C38" s="0">
+      <c r="C39" s="5">
         <v>1.534375</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="0">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="4">
         <v>0.37</v>
       </c>
-      <c r="B39" s="0">
+      <c r="B40" s="4">
         <v>1.5420200462606013</v>
       </c>
-      <c r="C39" s="0">
+      <c r="C40" s="5">
         <v>1.557936507936508</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="0">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="4">
         <v>0.38</v>
       </c>
-      <c r="B40" s="0">
+      <c r="B41" s="4">
         <v>1.5649452269170578</v>
       </c>
-      <c r="C40" s="0">
+      <c r="C41" s="5">
         <v>1.582258064516129</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="0">
-        <v>0.39000000000000001</v>
-      </c>
-      <c r="B41" s="0">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="4">
+        <v>0.39</v>
+      </c>
+      <c r="B42" s="4">
         <v>1.5885623510722797</v>
       </c>
-      <c r="C41" s="0">
+      <c r="C42" s="5">
         <v>1.6073770491803279</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="0">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="B42" s="0">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="B43" s="5">
         <v>1.6129032258064517</v>
       </c>
-      <c r="C42" s="0">
+      <c r="C43" s="5">
         <v>1.6333333333333333</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="0">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="5">
         <v>0.41000000000000003</v>
       </c>
-      <c r="B43" s="0">
+      <c r="B44" s="5">
         <v>1.6380016380016378</v>
       </c>
-      <c r="C43" s="0">
+      <c r="C44" s="5">
         <v>1.6601694915254239</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="0">
-        <v>0.41999999999999998</v>
-      </c>
-      <c r="B44" s="0">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="5">
+        <v>0.42</v>
+      </c>
+      <c r="B45" s="5">
         <v>1.6638935108153079</v>
       </c>
-      <c r="C44" s="0">
+      <c r="C45" s="5">
         <v>1.6879310344827583</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="0">
-        <v>0.42999999999999999</v>
-      </c>
-      <c r="B45" s="0">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="5">
+        <v>0.43</v>
+      </c>
+      <c r="B46" s="5">
         <v>1.6906170752324599</v>
       </c>
-      <c r="C45" s="0">
+      <c r="C46" s="5">
         <v>1.7166666666666666</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="0">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="5">
         <v>0.44</v>
       </c>
-      <c r="B46" s="0">
+      <c r="B47" s="5">
         <v>1.7182130584192439</v>
       </c>
-      <c r="C46" s="0">
+      <c r="C47" s="5">
         <v>1.7464285714285712</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="0">
-        <v>0.45000000000000001</v>
-      </c>
-      <c r="B47" s="0">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="B48" s="5">
         <v>1.7467248908296944</v>
       </c>
-      <c r="C47" s="0">
+      <c r="C48" s="5">
         <v>1.7772727272727271</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="0">
-        <v>0.46000000000000002</v>
-      </c>
-      <c r="B48" s="0">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="5">
+        <v>0.46</v>
+      </c>
+      <c r="B49" s="5">
         <v>1.7761989342806397</v>
       </c>
-      <c r="C48" s="0">
+      <c r="C49" s="5">
         <v>1.8092592592592591</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="0">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="5">
         <v>0.47000000000000003</v>
       </c>
-      <c r="B49" s="0">
+      <c r="B50" s="5">
         <v>1.8066847335140019</v>
       </c>
-      <c r="C49" s="0">
+      <c r="C50" s="5">
         <v>1.8424528301886791</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="0">
-        <v>0.47999999999999998</v>
-      </c>
-      <c r="B50" s="0">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="5">
+        <v>0.48</v>
+      </c>
+      <c r="B51" s="5">
         <v>1.838235294117647</v>
       </c>
-      <c r="C50" s="0">
+      <c r="C51" s="5">
         <v>1.8769230769230769</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="0">
-        <v>0.48999999999999999</v>
-      </c>
-      <c r="B51" s="0">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="5">
+        <v>0.49</v>
+      </c>
+      <c r="B52" s="5">
         <v>1.8709073900841908</v>
       </c>
-      <c r="C51" s="0">
+      <c r="C52" s="5">
         <v>1.9127450980392158</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="0">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="5">
         <v>0.5</v>
       </c>
-      <c r="B52" s="0">
+      <c r="B53" s="5">
         <v>1.9047619047619047</v>
       </c>
-      <c r="C52" s="0">
+      <c r="C53" s="5">
         <v>1.95</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="0">
-        <v>0.51000000000000001</v>
-      </c>
-      <c r="B53" s="0">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="5">
+        <v>0.51</v>
+      </c>
+      <c r="B54" s="5">
         <v>1.9398642095053344</v>
       </c>
-      <c r="C53" s="0">
+      <c r="C54" s="5">
         <v>1.9887755102040818</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="0">
-        <v>0.52000000000000002</v>
-      </c>
-      <c r="B54" s="0">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="5">
+        <v>0.52</v>
+      </c>
+      <c r="B55" s="5">
         <v>1.9762845849802371</v>
       </c>
-      <c r="C54" s="0">
+      <c r="C55" s="5">
         <v>2.0291666666666668</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="0">
-        <v>0.53000000000000003</v>
-      </c>
-      <c r="B55" s="0">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="B56" s="5">
         <v>2.0140986908358509</v>
       </c>
-      <c r="C55" s="0">
+      <c r="C56" s="5">
         <v>2.0712765957446808</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="0">
-        <v>0.54000000000000004</v>
-      </c>
-      <c r="B56" s="0">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="5">
+        <v>0.54</v>
+      </c>
+      <c r="B57" s="5">
         <v>2.0533880903490762</v>
       </c>
-      <c r="C56" s="0">
+      <c r="C57" s="5">
         <v>2.1152173913043479</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="0">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="5">
         <v>0.55000000000000004</v>
       </c>
-      <c r="B57" s="0">
+      <c r="B58" s="5">
         <v>2.0942408376963351</v>
       </c>
-      <c r="C57" s="0">
+      <c r="C58" s="5">
         <v>2.1611111111111114</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="0">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="5">
         <v>0.56000000000000005</v>
       </c>
-      <c r="B58" s="0">
+      <c r="B59" s="5">
         <v>2.1367521367521367</v>
       </c>
-      <c r="C58" s="0">
+      <c r="C59" s="5">
         <v>2.2090909090909094</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="0">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="5">
         <v>0.57000000000000006</v>
       </c>
-      <c r="B59" s="0">
+      <c r="B60" s="5">
         <v>2.1810250817884405</v>
       </c>
-      <c r="C59" s="0">
+      <c r="C60" s="5">
         <v>2.2593023255813955</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="0">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="5">
         <v>0.58000000000000007</v>
       </c>
-      <c r="B60" s="0">
+      <c r="B61" s="5">
         <v>2.2271714922049002</v>
       </c>
-      <c r="C60" s="0">
+      <c r="C61" s="5">
         <v>2.3119047619047621</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="0">
-        <v>0.58999999999999997</v>
-      </c>
-      <c r="B61" s="0">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="B62" s="5">
         <v>2.2753128555176336</v>
       </c>
-      <c r="C61" s="0">
+      <c r="C62" s="5">
         <v>2.3670731707317074</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="0">
-        <v>0.59999999999999998</v>
-      </c>
-      <c r="B62" s="0">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="B63" s="5">
         <v>2.3255813953488369</v>
       </c>
-      <c r="C62" s="0">
+      <c r="C63" s="5">
         <v>2.4249999999999998</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="0">
-        <v>0.60999999999999999</v>
-      </c>
-      <c r="B63" s="0">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="5">
+        <v>0.61</v>
+      </c>
+      <c r="B64" s="5">
         <v>2.3781212841854935</v>
       </c>
-      <c r="C63" s="0">
+      <c r="C64" s="5">
         <v>2.4858974358974359</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="0">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="5">
         <v>0.62</v>
       </c>
-      <c r="B64" s="0">
+      <c r="B65" s="5">
         <v>2.4330900243308999</v>
       </c>
-      <c r="C64" s="0">
+      <c r="C65" s="5">
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="0">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="5">
         <v>0.63</v>
       </c>
-      <c r="B65" s="0">
+      <c r="B66" s="5">
         <v>2.4906600249065995</v>
       </c>
-      <c r="C65" s="0">
+      <c r="C66" s="5">
         <v>2.6175675675675678</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="0">
-        <v>0.64000000000000001</v>
-      </c>
-      <c r="B66" s="0">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="5">
+        <v>0.64</v>
+      </c>
+      <c r="B67" s="5">
         <v>2.5510204081632653</v>
       </c>
-      <c r="C66" s="0">
+      <c r="C67" s="5">
         <v>2.6888888888888891</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="0">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="5">
         <v>0.64999999999999991</v>
       </c>
-      <c r="B67" s="0">
+      <c r="B68" s="5">
         <v>2.6143790849673199</v>
       </c>
-      <c r="C67" s="0">
+      <c r="C68" s="5">
         <v>2.7642857142857138</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="0">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="5">
         <v>0.65999999999999992</v>
       </c>
-      <c r="B68" s="0">
+      <c r="B69" s="5">
         <v>2.6809651474530822</v>
       </c>
-      <c r="C68" s="0">
+      <c r="C69" s="5">
         <v>2.8441176470588228</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="0">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="5">
         <v>0.66999999999999993</v>
       </c>
-      <c r="B69" s="0">
+      <c r="B70" s="5">
         <v>2.7510316368638237</v>
       </c>
-      <c r="C69" s="0">
+      <c r="C70" s="5">
         <v>2.9287878787878783</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="0">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="5">
         <v>0.67999999999999994</v>
       </c>
-      <c r="B70" s="0">
+      <c r="B71" s="5">
         <v>2.8248587570621462</v>
       </c>
-      <c r="C70" s="0">
+      <c r="C71" s="5">
         <v>3.0187499999999994</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="0">
-        <v>0.68999999999999995</v>
-      </c>
-      <c r="B71" s="0">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="5">
+        <v>0.69</v>
+      </c>
+      <c r="B72" s="5">
         <v>2.9027576197387517</v>
       </c>
-      <c r="C71" s="0">
+      <c r="C72" s="5">
         <v>3.1145161290322578</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="0">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="B72" s="0">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="B73" s="5">
         <v>2.9850746268656709</v>
       </c>
-      <c r="C72" s="0">
+      <c r="C73" s="5">
         <v>3.2166666666666659</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="0">
-        <v>0.70999999999999996</v>
-      </c>
-      <c r="B73" s="0">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="5">
+        <v>0.71</v>
+      </c>
+      <c r="B74" s="5">
         <v>3.0721966205837172</v>
       </c>
-      <c r="C73" s="0">
+      <c r="C74" s="5">
         <v>3.3258620689655167</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="0">
-        <v>0.71999999999999997</v>
-      </c>
-      <c r="B74" s="0">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="B75" s="5">
         <v>3.164556962025316</v>
       </c>
-      <c r="C74" s="0">
+      <c r="C75" s="5">
         <v>3.4428571428571426</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="0">
-        <v>0.72999999999999998</v>
-      </c>
-      <c r="B75" s="0">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="5">
+        <v>0.73</v>
+      </c>
+      <c r="B76" s="5">
         <v>3.2626427406199023</v>
       </c>
-      <c r="C75" s="0">
+      <c r="C76" s="5">
         <v>3.5685185185185184</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="0">
-        <v>0.73999999999999999</v>
-      </c>
-      <c r="B76" s="0">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="5">
+        <v>0.74</v>
+      </c>
+      <c r="B77" s="5">
         <v>3.3670033670033663</v>
       </c>
-      <c r="C76" s="0">
+      <c r="C77" s="5">
         <v>3.7038461538461536</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="0">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="5">
         <v>0.75</v>
       </c>
-      <c r="B77" s="0">
+      <c r="B78" s="5">
         <v>3.4782608695652164</v>
       </c>
-      <c r="C77" s="0">
-        <v>3.8500000000000001</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="0">
-        <v>0.76000000000000001</v>
-      </c>
-      <c r="B78" s="0">
+      <c r="C78" s="5">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="5">
+        <v>0.76</v>
+      </c>
+      <c r="B79" s="5">
         <v>3.5971223021582732</v>
       </c>
-      <c r="C78" s="0">
+      <c r="C79" s="5">
         <v>4.0083333333333337</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="0">
-        <v>0.77000000000000002</v>
-      </c>
-      <c r="B79" s="0">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="5">
+        <v>0.77</v>
+      </c>
+      <c r="B80" s="5">
         <v>3.724394785847299</v>
       </c>
-      <c r="C79" s="0">
+      <c r="C80" s="5">
         <v>4.1804347826086961</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="0">
-        <v>0.78000000000000003</v>
-      </c>
-      <c r="B80" s="0">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="B81" s="5">
         <v>3.8610038610038608</v>
       </c>
-      <c r="C80" s="0">
+      <c r="C81" s="5">
         <v>4.3681818181818182</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="0">
-        <v>0.79000000000000004</v>
-      </c>
-      <c r="B81" s="0">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="B82" s="5">
         <v>4.0080160320641269</v>
       </c>
-      <c r="C81" s="0">
+      <c r="C82" s="5">
         <v>4.5738095238095244</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="0">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="B82" s="0">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="B83" s="5">
         <v>4.166666666666667</v>
       </c>
-      <c r="C82" s="0">
+      <c r="C83" s="5">
         <v>4.8000000000000007</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="0">
-        <v>0.81000000000000005</v>
-      </c>
-      <c r="B83" s="0">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="B84" s="5">
         <v>4.3383947939262466</v>
       </c>
-      <c r="C83" s="0">
+      <c r="C84" s="5">
         <v>5.0500000000000016</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="0">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="5">
         <v>0.82000000000000006</v>
       </c>
-      <c r="B84" s="0">
+      <c r="B85" s="5">
         <v>4.5248868778280551</v>
       </c>
-      <c r="C84" s="0">
+      <c r="C85" s="5">
         <v>5.3277777777777793</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="0">
-        <v>0.82999999999999996</v>
-      </c>
-      <c r="B85" s="0">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="B86" s="5">
         <v>4.7281323877068555</v>
       </c>
-      <c r="C85" s="0">
+      <c r="C86" s="5">
         <v>5.6382352941176457</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="0">
-        <v>0.83999999999999997</v>
-      </c>
-      <c r="B86" s="0">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" s="5">
+        <v>0.84</v>
+      </c>
+      <c r="B87" s="5">
         <v>4.9504950495049487</v>
       </c>
-      <c r="C86" s="0">
+      <c r="C87" s="5">
         <v>5.9874999999999989</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="0">
-        <v>0.84999999999999998</v>
-      </c>
-      <c r="B87" s="0">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="B88" s="5">
         <v>5.1948051948051948</v>
       </c>
-      <c r="C87" s="0">
+      <c r="C88" s="5">
         <v>6.3833333333333329</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="0">
-        <v>0.85999999999999999</v>
-      </c>
-      <c r="B88" s="0">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" s="5">
+        <v>0.86</v>
+      </c>
+      <c r="B89" s="5">
         <v>5.464480874316938</v>
       </c>
-      <c r="C88" s="0">
+      <c r="C89" s="5">
         <v>6.8357142857142845</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="0">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="5">
         <v>0.87</v>
       </c>
-      <c r="B89" s="0">
+      <c r="B90" s="5">
         <v>5.7636887608069172</v>
       </c>
-      <c r="C89" s="0">
+      <c r="C90" s="5">
         <v>7.3576923076923073</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="0">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="5">
         <v>0.88</v>
       </c>
-      <c r="B90" s="0">
+      <c r="B91" s="5">
         <v>6.0975609756097544</v>
       </c>
-      <c r="C90" s="0">
+      <c r="C91" s="5">
         <v>7.9666666666666668</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="0">
-        <v>0.89000000000000001</v>
-      </c>
-      <c r="B91" s="0">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" s="5">
+        <v>0.89</v>
+      </c>
+      <c r="B92" s="5">
         <v>6.4724919093851101</v>
       </c>
-      <c r="C91" s="0">
+      <c r="C92" s="5">
         <v>8.6863636363636374</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="0">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="B92" s="0">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="B93" s="5">
         <v>6.8965517241379306</v>
       </c>
-      <c r="C92" s="0">
+      <c r="C93" s="5">
         <v>9.5500000000000025</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="0">
-        <v>0.91000000000000003</v>
-      </c>
-      <c r="B93" s="0">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="B94" s="5">
         <v>7.3800738007380042</v>
       </c>
-      <c r="C93" s="0">
+      <c r="C94" s="5">
         <v>10.60555555555556</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="0">
-        <v>0.92000000000000004</v>
-      </c>
-      <c r="B94" s="0">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="B95" s="5">
         <v>7.9365079365079367</v>
       </c>
-      <c r="C94" s="0">
+      <c r="C95" s="5">
         <v>11.925000000000006</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="0">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96" s="5">
         <v>0.92999999999999994</v>
       </c>
-      <c r="B95" s="0">
+      <c r="B96" s="5">
         <v>8.5836909871244593</v>
       </c>
-      <c r="C95" s="0">
+      <c r="C96" s="5">
         <v>13.621428571428559</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="0">
-        <v>0.93999999999999995</v>
-      </c>
-      <c r="B96" s="0">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" s="5">
+        <v>0.94</v>
+      </c>
+      <c r="B97" s="5">
         <v>9.3457943925233558</v>
       </c>
-      <c r="C96" s="0">
+      <c r="C97" s="5">
         <v>15.883333333333319</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="0">
-        <v>0.94999999999999996</v>
-      </c>
-      <c r="B97" s="0">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="B98" s="5">
         <v>10.256410256410254</v>
       </c>
-      <c r="C97" s="0">
+      <c r="C98" s="5">
         <v>19.049999999999983</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="0">
-        <v>0.95999999999999996</v>
-      </c>
-      <c r="B98" s="0">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="B99" s="5">
         <v>11.363636363636354</v>
       </c>
-      <c r="C98" s="0">
+      <c r="C99" s="5">
         <v>23.799999999999979</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="0">
-        <v>0.96999999999999997</v>
-      </c>
-      <c r="B99" s="0">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" s="5">
+        <v>0.97</v>
+      </c>
+      <c r="B100" s="5">
         <v>12.738853503184711</v>
       </c>
-      <c r="C99" s="0">
+      <c r="C100" s="5">
         <v>31.71666666666664</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="0">
-        <v>0.97999999999999998</v>
-      </c>
-      <c r="B100" s="0">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" s="5">
+        <v>0.98</v>
+      </c>
+      <c r="B101" s="5">
         <v>14.492753623188394</v>
       </c>
-      <c r="C100" s="0">
+      <c r="C101" s="5">
         <v>47.549999999999955</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="0">
-        <v>0.98999999999999999</v>
-      </c>
-      <c r="B101" s="0">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" s="5">
+        <v>0.99</v>
+      </c>
+      <c r="B102" s="5">
         <v>16.806722689075631</v>
       </c>
-      <c r="C101" s="0">
+      <c r="C102" s="5">
         <v>95.049999999999912</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="0">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" s="5">
         <v>1</v>
       </c>
-      <c r="B102" s="0">
+      <c r="B103" s="5">
         <v>19.999999999999982</v>
       </c>
-      <c r="C102" s="0">
+      <c r="C103" s="5">
         <v>65535</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>